--- a/marketing-tracker/tracker_template.xlsx
+++ b/marketing-tracker/tracker_template.xlsx
@@ -7091,7 +7091,7 @@
       <formula1>=Lists!$A$2:$A$3</formula1>
     </dataValidation>
     <dataValidation sqref="E2:E501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not an allowed value" error="Pick a vertical from the dropdown (see the Lists tab)." type="list">
-      <formula1>=Lists!$B$2:$B$9</formula1>
+      <formula1>=Lists!$B$2:$B$11</formula1>
     </dataValidation>
     <dataValidation sqref="H2:H501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not an allowed value" error="Pick a campaign_type from the dropdown (see the Lists tab)." type="list">
       <formula1>=Lists!$C$2:$C$11</formula1>
@@ -7414,36 +7414,66 @@
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
+          <t>Royal Club</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Royal Club</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>RCL</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Snoonu Plus</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Adoption</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Snoonu Plus</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>SPL</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
           <t>Cross-vertical</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Habit Builder</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
         <is>
           <t>Cross-vertical</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>CVT</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Adoption</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Habit Builder</t>
         </is>
       </c>
     </row>
